--- a/artfynd/A 43450-2022 artfynd.xlsx
+++ b/artfynd/A 43450-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43450-2022 artfynd.xlsx
+++ b/artfynd/A 43450-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104593210</v>
+        <v>106012804</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dals-Ed, Dls</t>
+          <t>Holane, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>313275.0702186072</v>
+        <v>313304</v>
       </c>
       <c r="R2" t="n">
-        <v>6525835.641244652</v>
+        <v>6525763</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:12</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:12</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -791,12 +775,7 @@
         <v>106012805</v>
       </c>
       <c r="B3" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>313082.2508838365</v>
+        <v>313083</v>
       </c>
       <c r="R3" t="n">
-        <v>6525758.379319079</v>
+        <v>6525758</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -861,19 +840,9 @@
           <t>2023-01-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106012763</v>
+        <v>106012806</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>313167.1306628212</v>
+        <v>313174</v>
       </c>
       <c r="R4" t="n">
-        <v>6525698.270140647</v>
+        <v>6526074</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -973,24 +937,9 @@
           <t>2023-01-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106012783</v>
+        <v>106012807</v>
       </c>
       <c r="B5" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1057,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>313286.5858210867</v>
+        <v>313264</v>
       </c>
       <c r="R5" t="n">
-        <v>6525783.751513453</v>
+        <v>6526060</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1090,19 +1034,9 @@
           <t>2023-01-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106012762</v>
+        <v>106012808</v>
       </c>
       <c r="B6" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1145,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>313234.4760248136</v>
+        <v>313499</v>
       </c>
       <c r="R6" t="n">
-        <v>6525801.827414651</v>
+        <v>6526041</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1202,19 +1131,9 @@
           <t>2023-01-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-01-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106012812</v>
+        <v>106012809</v>
       </c>
       <c r="B7" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>313234.4760248136</v>
+        <v>313048</v>
       </c>
       <c r="R7" t="n">
-        <v>6525801.827414651</v>
+        <v>6525758</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1314,19 +1228,9 @@
           <t>2023-01-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-01-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>106012753</v>
+        <v>106012812</v>
       </c>
       <c r="B8" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1393,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>313432.6596527715</v>
+        <v>313235</v>
       </c>
       <c r="R8" t="n">
-        <v>6526022.458527009</v>
+        <v>6525802</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1423,22 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106012736</v>
+        <v>106012749</v>
       </c>
       <c r="B9" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1505,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>313131.84976533</v>
+        <v>313216</v>
       </c>
       <c r="R9" t="n">
-        <v>6525785.015555262</v>
+        <v>6526103</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1535,22 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-01-12</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-01-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>106012808</v>
+        <v>106012753</v>
       </c>
       <c r="B10" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1617,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>313498.485255949</v>
+        <v>313433</v>
       </c>
       <c r="R10" t="n">
-        <v>6526041.054116609</v>
+        <v>6526022</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1647,22 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-01-12</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-01-12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106012741</v>
+        <v>106012762</v>
       </c>
       <c r="B11" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1729,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>313353</v>
+        <v>313235</v>
       </c>
       <c r="R11" t="n">
-        <v>6525957</v>
+        <v>6525802</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1759,17 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
+          <t>2023-01-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2023-01-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106012749</v>
+        <v>106012726</v>
       </c>
       <c r="B12" t="n">
-        <v>94838</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1812,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1836,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>313215.7750837175</v>
+        <v>313317</v>
       </c>
       <c r="R12" t="n">
-        <v>6526102.422324139</v>
+        <v>6525781</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1869,19 +1713,9 @@
           <t>2023-01-14</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106012807</v>
+        <v>106012735</v>
       </c>
       <c r="B13" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1924,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1948,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>313264.631887692</v>
+        <v>313503</v>
       </c>
       <c r="R13" t="n">
-        <v>6526060.135954638</v>
+        <v>6526078</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1978,22 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2020,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>106012766</v>
+        <v>106012736</v>
       </c>
       <c r="B14" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2060,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>313359.8687307891</v>
+        <v>313132</v>
       </c>
       <c r="R14" t="n">
-        <v>6525956.499614077</v>
+        <v>6525785</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2090,27 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2023-01-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2137,53 +1936,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>106012806</v>
+        <v>104593210</v>
       </c>
       <c r="B15" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Holane, Dls</t>
+          <t>Dals-Ed, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>313173.3604954262</v>
+        <v>313276</v>
       </c>
       <c r="R15" t="n">
-        <v>6526073.884586159</v>
+        <v>6525835</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2207,22 +2002,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,27 +2032,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>106012767</v>
+        <v>106012783</v>
       </c>
       <c r="B16" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2265,21 +2055,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2289,10 +2079,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>313102.4658403115</v>
+        <v>313287</v>
       </c>
       <c r="R16" t="n">
-        <v>6525832.585792881</v>
+        <v>6525783</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2322,24 +2112,9 @@
           <t>2023-01-14</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2363,6 +2138,914 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>106012784</v>
+      </c>
+      <c r="B17" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Holane, Dls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>313239</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6525697</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>106012763</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Holane, Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>313167</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6525698</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Läte</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>106012766</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Holane, Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>313360</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6525956</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>106012767</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Holane, Dls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>313102</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6525832</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>106012741</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Holane, Dls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>313353</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6525957</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>106012742</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Holane, Dls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>313387</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6525969</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>106012743</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Holane, Dls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>313382</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6525987</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>106012745</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Holane, Dls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>313137</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6525728</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>106012746</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Holane, Dls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>313206</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6525781</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Töftedal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-01-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-01-12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43450-2022 artfynd.xlsx
+++ b/artfynd/A 43450-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012804</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012805</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012806</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012807</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012808</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012809</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012812</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012749</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012753</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012762</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012726</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012735</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012736</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2041,6 +2111,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104593210</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2138,6 +2213,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012783</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2235,6 +2315,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012784</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2337,6 +2422,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012763</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2439,6 +2529,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012766</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2541,6 +2636,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012767</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2643,6 +2743,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012741</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2745,6 +2850,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012742</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2847,6 +2957,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012743</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2949,6 +3064,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012745</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3046,8 +3166,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106012746</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>